--- a/R/Scripts/matings/genus_results.xlsx
+++ b/R/Scripts/matings/genus_results.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucascamacho/Dropbox/Doc/Code/evowm/R/Scripts/matings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A599944-CC24-CB46-A0BB-B6CB93BC5EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91AC74E-68EC-F449-BEBD-8C57E7935FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{41D2D77F-E09E-6C4F-BC4A-8BBD63B28252}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{41D2D77F-E09E-6C4F-BC4A-8BBD63B28252}"/>
   </bookViews>
   <sheets>
     <sheet name="FM" sheetId="1" r:id="rId1"/>
-    <sheet name="integration" sheetId="2" r:id="rId2"/>
-    <sheet name="size" sheetId="3" r:id="rId3"/>
+    <sheet name="normal" sheetId="4" r:id="rId2"/>
+    <sheet name="integration" sheetId="2" r:id="rId3"/>
+    <sheet name="size" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="268">
   <si>
     <t>PGLS</t>
   </si>
@@ -611,6 +612,237 @@
   </si>
   <si>
     <t>0.41</t>
+  </si>
+  <si>
+    <t>Phylogenetic Half-Life (Myr)</t>
+  </si>
+  <si>
+    <t>Integration + NMDS1 + NMDS2</t>
+  </si>
+  <si>
+    <t>Integration + NMDS1 + NMDS2 + Size</t>
+  </si>
+  <si>
+    <t>OU model selection across primates clades (ΔAICc &lt; 2)</t>
+  </si>
+  <si>
+    <t>0.0000073</t>
+  </si>
+  <si>
+    <t>884889.2</t>
+  </si>
+  <si>
+    <t>6.43</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>0.0144</t>
+  </si>
+  <si>
+    <t>0.0851</t>
+  </si>
+  <si>
+    <t>8.13</t>
+  </si>
+  <si>
+    <t>0.00000019</t>
+  </si>
+  <si>
+    <t>22.2</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>11.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate </t>
+  </si>
+  <si>
+    <t>1.334</t>
+  </si>
+  <si>
+    <t>-2.826</t>
+  </si>
+  <si>
+    <t>-0.300</t>
+  </si>
+  <si>
+    <t>0.778</t>
+  </si>
+  <si>
+    <t>-0.297</t>
+  </si>
+  <si>
+    <t>0.396</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>0.794</t>
+  </si>
+  <si>
+    <t>0.313</t>
+  </si>
+  <si>
+    <t>0.627</t>
+  </si>
+  <si>
+    <t>0.457</t>
+  </si>
+  <si>
+    <t>3.368</t>
+  </si>
+  <si>
+    <t>-6.277</t>
+  </si>
+  <si>
+    <t>-3.558</t>
+  </si>
+  <si>
+    <t>-0.960</t>
+  </si>
+  <si>
+    <t>1.241</t>
+  </si>
+  <si>
+    <t>-0.651</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>0.345</t>
+  </si>
+  <si>
+    <t>0.224</t>
+  </si>
+  <si>
+    <t>PGLS model including the Parvorder effect (λ = 0.970)</t>
+  </si>
+  <si>
+    <t>PGLS model selection (ΔAICc &lt; 2)</t>
+  </si>
+  <si>
+    <t>R²</t>
+  </si>
+  <si>
+    <t>Integration + Size + NMDS1</t>
+  </si>
+  <si>
+    <t>Integration + Size + NMDS2</t>
+  </si>
+  <si>
+    <t>14.103</t>
+  </si>
+  <si>
+    <t>15.572</t>
+  </si>
+  <si>
+    <t>0.732</t>
+  </si>
+  <si>
+    <t>0.738</t>
+  </si>
+  <si>
+    <t>0.954</t>
+  </si>
+  <si>
+    <t>1.470</t>
+  </si>
+  <si>
+    <t>-8.529</t>
+  </si>
+  <si>
+    <t>1.311</t>
+  </si>
+  <si>
+    <t>Phylogenetic ANOVA Results</t>
+  </si>
+  <si>
+    <t>Mating System</t>
+  </si>
+  <si>
+    <t>5.30</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>4.51</t>
+  </si>
+  <si>
+    <t>3.69</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>2.64</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>2.34</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>0.333</t>
+  </si>
+  <si>
+    <t>0.371</t>
+  </si>
+  <si>
+    <t>0.580</t>
+  </si>
+  <si>
+    <t>0.012</t>
+  </si>
+  <si>
+    <t>0.018</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>0.473</t>
+  </si>
+  <si>
+    <t>0.626</t>
+  </si>
+  <si>
+    <t>0.676</t>
+  </si>
+  <si>
+    <t>0.806</t>
+  </si>
+  <si>
+    <t>5.64</t>
+  </si>
+  <si>
+    <t>5.01</t>
+  </si>
+  <si>
+    <t>6.02</t>
+  </si>
+  <si>
+    <t>4.24</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>0.18</t>
+  </si>
+  <si>
+    <t>0.06</t>
   </si>
 </sst>
 </file>
@@ -826,7 +1058,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -930,6 +1162,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -963,28 +1213,47 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1373,14 +1642,14 @@
       <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
       <c r="M4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1407,11 +1676,11 @@
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
       <c r="F5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1430,18 +1699,18 @@
       <c r="K5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="35" t="s">
+      <c r="M5" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="S5" s="35" t="s">
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="S5" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="T5" s="35"/>
-      <c r="U5" s="35"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B6" s="8" t="s">
@@ -1453,14 +1722,14 @@
       <c r="D6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="41"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="47"/>
       <c r="M6" s="4" t="s">
         <v>15</v>
       </c>
@@ -1476,10 +1745,10 @@
       <c r="Q6" s="7">
         <v>3646655</v>
       </c>
-      <c r="S6" s="49" t="s">
+      <c r="S6" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="T6" s="50" t="s">
+      <c r="T6" s="37" t="s">
         <v>166</v>
       </c>
       <c r="U6" s="16" t="s">
@@ -1529,13 +1798,13 @@
       <c r="Q7" s="22">
         <v>2196387</v>
       </c>
-      <c r="S7" s="49" t="s">
+      <c r="S7" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="T7" s="50" t="s">
+      <c r="T7" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="U7" s="46" t="s">
+      <c r="U7" s="35" t="s">
         <v>180</v>
       </c>
     </row>
@@ -1555,20 +1824,20 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
-      <c r="M8" s="36" t="s">
+      <c r="M8" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="38"/>
-      <c r="S8" s="49" t="s">
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="44"/>
+      <c r="S8" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="T8" s="50" t="s">
+      <c r="T8" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="U8" s="46" t="s">
+      <c r="U8" s="35" t="s">
         <v>163</v>
       </c>
     </row>
@@ -1603,10 +1872,10 @@
       <c r="Q9" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="S9" s="49" t="s">
+      <c r="S9" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="T9" s="50" t="s">
+      <c r="T9" s="37" t="s">
         <v>174</v>
       </c>
       <c r="U9" s="16" t="s">
@@ -1614,9 +1883,9 @@
       </c>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
       <c r="F10" s="6"/>
       <c r="G10" s="5"/>
       <c r="H10" s="6"/>
@@ -1638,10 +1907,10 @@
       <c r="Q10" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="S10" s="49" t="s">
+      <c r="S10" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="T10" s="50" t="s">
+      <c r="T10" s="37" t="s">
         <v>174</v>
       </c>
       <c r="U10" s="16" t="s">
@@ -1664,10 +1933,10 @@
       <c r="Q11" s="13">
         <v>377592</v>
       </c>
-      <c r="S11" s="49" t="s">
+      <c r="S11" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="T11" s="50" t="s">
+      <c r="T11" s="37" t="s">
         <v>181</v>
       </c>
       <c r="U11" s="16" t="s">
@@ -1680,10 +1949,10 @@
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
-      <c r="S12" s="49" t="s">
+      <c r="S12" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="T12" s="50" t="s">
+      <c r="T12" s="37" t="s">
         <v>185</v>
       </c>
       <c r="U12" s="16" t="s">
@@ -1699,13 +1968,13 @@
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
-      <c r="S13" s="49" t="s">
+      <c r="S13" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="T13" s="50" t="s">
+      <c r="T13" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="U13" s="46" t="s">
+      <c r="U13" s="35" t="s">
         <v>188</v>
       </c>
     </row>
@@ -1725,13 +1994,13 @@
       <c r="J14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="S14" s="49" t="s">
+      <c r="S14" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="T14" s="50" t="s">
+      <c r="T14" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="U14" s="46" t="s">
+      <c r="U14" s="35" t="s">
         <v>190</v>
       </c>
     </row>
@@ -1751,11 +2020,11 @@
       <c r="J15" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="S15" s="35" t="s">
+      <c r="S15" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
+      <c r="T15" s="41"/>
+      <c r="U15" s="41"/>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="F16" s="4" t="s">
@@ -1773,10 +2042,10 @@
       <c r="J16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="S16" s="49" t="s">
+      <c r="S16" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="T16" s="50" t="s">
+      <c r="T16" s="37" t="s">
         <v>167</v>
       </c>
       <c r="U16" s="17" t="s">
@@ -1799,10 +2068,10 @@
       <c r="J17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="S17" s="49" t="s">
+      <c r="S17" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="T17" s="50" t="s">
+      <c r="T17" s="37" t="s">
         <v>169</v>
       </c>
       <c r="U17" s="16" t="s">
@@ -1825,10 +2094,10 @@
       <c r="J18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="S18" s="49" t="s">
+      <c r="S18" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="T18" s="50" t="s">
+      <c r="T18" s="37" t="s">
         <v>172</v>
       </c>
       <c r="U18" s="16" t="s">
@@ -1851,13 +2120,13 @@
       <c r="J19" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="S19" s="49" t="s">
+      <c r="S19" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="T19" s="50" t="s">
+      <c r="T19" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="U19" s="46" t="s">
+      <c r="U19" s="35" t="s">
         <v>177</v>
       </c>
     </row>
@@ -1877,32 +2146,32 @@
       <c r="J20" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="S20" s="49" t="s">
+      <c r="S20" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="T20" s="50" t="s">
+      <c r="T20" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="U20" s="46" t="s">
+      <c r="U20" s="35" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="21" spans="6:21" x14ac:dyDescent="0.2">
-      <c r="S21" s="49" t="s">
+      <c r="S21" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="T21" s="50" t="s">
+      <c r="T21" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="U21" s="46" t="s">
+      <c r="U21" s="35" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="22" spans="6:21" x14ac:dyDescent="0.2">
-      <c r="S22" s="49" t="s">
+      <c r="S22" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="T22" s="50" t="s">
+      <c r="T22" s="37" t="s">
         <v>187</v>
       </c>
       <c r="U22" s="16" t="s">
@@ -1910,10 +2179,10 @@
       </c>
     </row>
     <row r="23" spans="6:21" x14ac:dyDescent="0.2">
-      <c r="S23" s="49" t="s">
+      <c r="S23" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="T23" s="50" t="s">
+      <c r="T23" s="37" t="s">
         <v>187</v>
       </c>
       <c r="U23" s="16" t="s">
@@ -1921,13 +2190,13 @@
       </c>
     </row>
     <row r="24" spans="6:21" x14ac:dyDescent="0.2">
-      <c r="S24" s="51" t="s">
+      <c r="S24" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="T24" s="52" t="s">
+      <c r="T24" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="U24" s="53" t="s">
+      <c r="U24" s="40" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1947,6 +2216,592 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C0EB34-5C4A-D443-A1F7-912E9592B05E}">
+  <dimension ref="B2:W24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B2" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="H2" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="N2" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="53"/>
+    </row>
+    <row r="3" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H3" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="65" t="s">
+        <v>206</v>
+      </c>
+      <c r="J3" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="65" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="65" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U3" s="66" t="s">
+        <v>240</v>
+      </c>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+    </row>
+    <row r="4" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B4" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="H4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="J4" s="54" t="s">
+        <v>212</v>
+      </c>
+      <c r="K4" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
+      <c r="U4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="54">
+        <v>23</v>
+      </c>
+      <c r="D5" s="54">
+        <v>0</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="59">
+        <v>-5.3999999999999999E-2</v>
+      </c>
+      <c r="J5" s="54" t="s">
+        <v>213</v>
+      </c>
+      <c r="K5" s="60" t="s">
+        <v>219</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O5" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="P5" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q5" s="54" t="s">
+        <v>236</v>
+      </c>
+      <c r="R5" s="54">
+        <v>0</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="U5" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B6" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="H6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="J6" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="K6" s="60" t="s">
+        <v>220</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="O6" s="54" t="s">
+        <v>233</v>
+      </c>
+      <c r="P6" s="54" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q6" s="54">
+        <v>1</v>
+      </c>
+      <c r="R6" s="54" t="s">
+        <v>237</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="U6" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="V6" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="W6" s="16" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="54">
+        <v>0</v>
+      </c>
+      <c r="E7" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H7" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="J7" s="52" t="s">
+        <v>215</v>
+      </c>
+      <c r="K7" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="N7" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="U7" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="V7" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="W7" s="16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B8" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" s="54" t="s">
+        <v>200</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H8" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="J8" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="K8" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="L8" s="62" t="s">
+        <v>226</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="R8" s="12">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="U8" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="V8" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="W8" s="35" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B9" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="54" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="7">
+        <v>36113586</v>
+      </c>
+      <c r="H9" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="64" t="s">
+        <v>211</v>
+      </c>
+      <c r="J9" s="55" t="s">
+        <v>217</v>
+      </c>
+      <c r="K9" s="64" t="s">
+        <v>223</v>
+      </c>
+      <c r="L9" s="13">
+        <v>52</v>
+      </c>
+      <c r="U9" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="V9" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="W9" s="35" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B10" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="U10" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="V10" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="W10" s="35" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B11" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="D11" s="56">
+        <v>0</v>
+      </c>
+      <c r="E11" s="55" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="U11" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="V11" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="W11" s="35" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="U12" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="V12" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="W12" s="35" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="U13" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="V13" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="W13" s="35" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="U14" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="V14" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="W14" s="35" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="U15" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="V15" s="43"/>
+      <c r="W15" s="44"/>
+    </row>
+    <row r="16" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="U16" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="V16" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="W16" s="16" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="U17" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="V17" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="W17" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="U18" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="V18" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="W18" s="16" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="U19" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="V19" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="W19" s="35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="U20" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="V20" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="W20" s="35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="U21" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="V21" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="W21" s="35" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="U22" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="V22" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="W22" s="35" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="23" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="U23" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="V23" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="W23" s="35" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="U24" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="V24" s="39" t="s">
+        <v>267</v>
+      </c>
+      <c r="W24" s="40" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="U5:W5"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N7:S7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA526B2-C61A-5F4F-AC86-1A0FD8B06582}">
   <dimension ref="B3:Q21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1999,14 +2854,14 @@
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
       <c r="M5" s="2" t="s">
         <v>2</v>
       </c>
@@ -2024,11 +2879,11 @@
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
       <c r="F6" s="4" t="s">
         <v>87</v>
       </c>
@@ -2047,13 +2902,13 @@
       <c r="K6" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="M6" s="35" t="s">
+      <c r="M6" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B7" s="8" t="s">
@@ -2109,21 +2964,21 @@
       <c r="D8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="41"/>
-      <c r="M8" s="42" t="s">
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="47"/>
+      <c r="M8" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="38"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="44"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
@@ -2202,34 +3057,34 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
       <c r="F11" s="6"/>
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="47"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="M12" s="47"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="M13" s="47"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.2">
       <c r="F14" s="15" t="s">
@@ -2369,7 +3224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312CDA36-46BD-4D46-A4C1-BA2213FB6E12}">
   <dimension ref="B3:Q21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2421,14 +3276,14 @@
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
       <c r="M5" s="2" t="s">
         <v>2</v>
       </c>
@@ -2446,11 +3301,11 @@
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
       <c r="F6" s="23" t="s">
         <v>87</v>
       </c>
@@ -2469,13 +3324,13 @@
       <c r="K6" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M6" s="35" t="s">
+      <c r="M6" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B7" s="8" t="s">
@@ -2531,21 +3386,21 @@
       <c r="D8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="43" t="s">
+      <c r="F8" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="45"/>
-      <c r="M8" s="42" t="s">
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="51"/>
+      <c r="M8" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="38"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="44"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
@@ -2627,9 +3482,9 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
       <c r="F11" s="6"/>
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>

--- a/R/Scripts/matings/genus_results.xlsx
+++ b/R/Scripts/matings/genus_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucascamacho/Dropbox/Doc/Code/evowm/R/Scripts/matings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91AC74E-68EC-F449-BEBD-8C57E7935FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014A016F-172F-374C-AA4F-44586086DD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{41D2D77F-E09E-6C4F-BC4A-8BBD63B28252}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{41D2D77F-E09E-6C4F-BC4A-8BBD63B28252}"/>
   </bookViews>
   <sheets>
     <sheet name="FM" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="288">
   <si>
     <t>PGLS</t>
   </si>
@@ -843,6 +843,66 @@
   </si>
   <si>
     <t>0.06</t>
+  </si>
+  <si>
+    <t>adjusted p (FDR)</t>
+  </si>
+  <si>
+    <t>0.149</t>
+  </si>
+  <si>
+    <t>0.164</t>
+  </si>
+  <si>
+    <t>0.417</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>0.757</t>
+  </si>
+  <si>
+    <t>0.773</t>
+  </si>
+  <si>
+    <t>0.126</t>
+  </si>
+  <si>
+    <t>0.191</t>
+  </si>
+  <si>
+    <t>0.296</t>
+  </si>
+  <si>
+    <t>0.518</t>
+  </si>
+  <si>
+    <t>0.890</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>0.178</t>
+  </si>
+  <si>
+    <t>0.180</t>
+  </si>
+  <si>
+    <t>0.195</t>
+  </si>
+  <si>
+    <t>0.257</t>
+  </si>
+  <si>
+    <t>0.574</t>
+  </si>
+  <si>
+    <t>0.700</t>
   </si>
 </sst>
 </file>
@@ -901,7 +961,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1054,11 +1114,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1180,6 +1264,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1202,6 +1290,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1213,47 +1304,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1590,7 +1653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E042300B-F734-714C-B163-A528E0097BE3}">
-  <dimension ref="B2:U24"/>
+  <dimension ref="B2:V24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -1599,14 +1662,15 @@
     <col min="16" max="16" width="16.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1632,7 +1696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1642,14 +1706,14 @@
       <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
       <c r="M4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1665,22 +1729,25 @@
       <c r="Q4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="S4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="T4" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="U4" s="15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B5" s="41" t="s">
+      <c r="V4" s="55" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B5" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
       <c r="F5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1699,20 +1766,21 @@
       <c r="K5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="41" t="s">
+      <c r="M5" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-      <c r="S5" s="41" t="s">
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="S5" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="T5" s="41"/>
-      <c r="U5" s="41"/>
-    </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T5" s="45"/>
+      <c r="U5" s="45"/>
+      <c r="V5" s="46"/>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B6" s="8" t="s">
         <v>15</v>
       </c>
@@ -1722,14 +1790,14 @@
       <c r="D6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="47"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="49"/>
       <c r="M6" s="4" t="s">
         <v>15</v>
       </c>
@@ -1748,14 +1816,17 @@
       <c r="S6" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="T6" s="37" t="s">
+      <c r="T6" s="59" t="s">
         <v>166</v>
       </c>
       <c r="U6" s="16" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V6" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
         <v>18</v>
       </c>
@@ -1801,14 +1872,17 @@
       <c r="S7" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="T7" s="37" t="s">
+      <c r="T7" s="59" t="s">
         <v>168</v>
       </c>
       <c r="U7" s="35" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
@@ -1824,24 +1898,27 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
-      <c r="M8" s="42" t="s">
+      <c r="M8" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="44"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="45"/>
+      <c r="Q8" s="46"/>
       <c r="S8" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="T8" s="37" t="s">
+      <c r="T8" s="59" t="s">
         <v>171</v>
       </c>
       <c r="U8" s="35" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="7" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B9" s="11" t="s">
         <v>20</v>
       </c>
@@ -1875,17 +1952,20 @@
       <c r="S9" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="T9" s="37" t="s">
+      <c r="T9" s="59" t="s">
         <v>174</v>
       </c>
       <c r="U9" s="16" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
+      <c r="V9" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
       <c r="F10" s="6"/>
       <c r="G10" s="5"/>
       <c r="H10" s="6"/>
@@ -1910,14 +1990,17 @@
       <c r="S10" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="T10" s="37" t="s">
+      <c r="T10" s="59" t="s">
         <v>174</v>
       </c>
       <c r="U10" s="16" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
       <c r="M11" s="11" t="s">
         <v>71</v>
       </c>
@@ -1936,14 +2019,17 @@
       <c r="S11" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="T11" s="37" t="s">
+      <c r="T11" s="59" t="s">
         <v>181</v>
       </c>
       <c r="U11" s="16" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
       <c r="M12" s="6"/>
       <c r="N12" s="5"/>
       <c r="O12" s="6"/>
@@ -1952,14 +2038,17 @@
       <c r="S12" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="T12" s="37" t="s">
+      <c r="T12" s="59" t="s">
         <v>185</v>
       </c>
       <c r="U12" s="16" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
       <c r="F13" s="15" t="s">
         <v>0</v>
       </c>
@@ -1971,14 +2060,17 @@
       <c r="S13" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="T13" s="37" t="s">
+      <c r="T13" s="59" t="s">
         <v>106</v>
       </c>
       <c r="U13" s="35" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
       <c r="F14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1997,14 +2089,17 @@
       <c r="S14" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="T14" s="37" t="s">
+      <c r="T14" s="59" t="s">
         <v>189</v>
       </c>
       <c r="U14" s="35" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
       <c r="F15" s="8" t="s">
         <v>27</v>
       </c>
@@ -2020,13 +2115,14 @@
       <c r="J15" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="S15" s="41" t="s">
+      <c r="S15" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T15" s="45"/>
+      <c r="U15" s="45"/>
+      <c r="V15" s="46"/>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
       <c r="F16" s="4" t="s">
         <v>15</v>
       </c>
@@ -2045,14 +2141,17 @@
       <c r="S16" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="T16" s="37" t="s">
+      <c r="T16" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="U16" s="17" t="s">
+      <c r="U16" s="16" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="16" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="6:22" x14ac:dyDescent="0.2">
       <c r="F17" s="4" t="s">
         <v>18</v>
       </c>
@@ -2071,14 +2170,17 @@
       <c r="S17" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="T17" s="37" t="s">
+      <c r="T17" s="59" t="s">
         <v>169</v>
       </c>
       <c r="U17" s="16" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="18" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="16" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="18" spans="6:22" x14ac:dyDescent="0.2">
       <c r="F18" s="4" t="s">
         <v>19</v>
       </c>
@@ -2097,14 +2199,17 @@
       <c r="S18" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="T18" s="37" t="s">
+      <c r="T18" s="59" t="s">
         <v>172</v>
       </c>
       <c r="U18" s="16" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="19" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="16" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="6:22" x14ac:dyDescent="0.2">
       <c r="F19" s="4" t="s">
         <v>20</v>
       </c>
@@ -2123,14 +2228,17 @@
       <c r="S19" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="T19" s="37" t="s">
+      <c r="T19" s="59" t="s">
         <v>176</v>
       </c>
       <c r="U19" s="35" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="20" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="7" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="20" spans="6:22" x14ac:dyDescent="0.2">
       <c r="F20" s="11" t="s">
         <v>31</v>
       </c>
@@ -2149,47 +2257,59 @@
       <c r="S20" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="T20" s="37" t="s">
+      <c r="T20" s="59" t="s">
         <v>178</v>
       </c>
       <c r="U20" s="35" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="21" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="21" spans="6:22" x14ac:dyDescent="0.2">
       <c r="S21" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="T21" s="37" t="s">
+      <c r="T21" s="59" t="s">
         <v>183</v>
       </c>
       <c r="U21" s="35" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="22" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="22" spans="6:22" x14ac:dyDescent="0.2">
       <c r="S22" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="T22" s="37" t="s">
+      <c r="T22" s="59" t="s">
         <v>187</v>
       </c>
       <c r="U22" s="16" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="23" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="23" spans="6:22" x14ac:dyDescent="0.2">
       <c r="S23" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="T23" s="37" t="s">
+      <c r="T23" s="59" t="s">
         <v>187</v>
       </c>
       <c r="U23" s="16" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="24" spans="6:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="6:22" x14ac:dyDescent="0.2">
       <c r="S24" s="38" t="s">
         <v>162</v>
       </c>
@@ -2199,17 +2319,20 @@
       <c r="U24" s="40" t="s">
         <v>96</v>
       </c>
+      <c r="V24" s="13" t="s">
+        <v>287</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="S5:U5"/>
-    <mergeCell ref="S15:U15"/>
     <mergeCell ref="F4:K4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="F6:K6"/>
+    <mergeCell ref="S15:V15"/>
+    <mergeCell ref="S5:V5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2217,7 +2340,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C0EB34-5C4A-D443-A1F7-912E9592B05E}">
-  <dimension ref="B2:W24"/>
+  <dimension ref="B2:X24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="49.1640625" bestFit="1" customWidth="1"/>
@@ -2225,9 +2348,10 @@
     <col min="6" max="6" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" s="15" t="s">
         <v>194</v>
       </c>
@@ -2235,13 +2359,13 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="43" t="s">
         <v>227</v>
       </c>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
       <c r="N2" s="15" t="s">
         <v>228</v>
       </c>
@@ -2249,9 +2373,9 @@
       <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
-      <c r="S2" s="53"/>
-    </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="S2" s="41"/>
+    </row>
+    <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2267,25 +2391,25 @@
       <c r="F3" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H3" s="65" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="65" t="s">
+      <c r="I3" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="J3" s="65" t="s">
+      <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="65" t="s">
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="65" t="s">
+      <c r="L3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="65" t="s">
+      <c r="N3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="65" t="s">
+      <c r="O3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="P3" s="3" t="s">
@@ -2300,64 +2424,68 @@
       <c r="S3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="U3" s="66" t="s">
+      <c r="U3" s="51" t="s">
         <v>240</v>
       </c>
-      <c r="V3" s="66"/>
-      <c r="W3" s="66"/>
-    </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B4" s="41" t="s">
+      <c r="V3" s="51"/>
+      <c r="W3" s="51"/>
+      <c r="X3" s="51"/>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B4" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
       <c r="H4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="54" t="s">
+      <c r="I4" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="54" t="s">
+      <c r="J4" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="K4" s="54" t="s">
+      <c r="K4" s="6" t="s">
         <v>218</v>
       </c>
       <c r="L4" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="N4" s="48" t="s">
+      <c r="N4" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
-      <c r="U4" s="1" t="s">
+      <c r="O4" s="45"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="45"/>
+      <c r="R4" s="45"/>
+      <c r="S4" s="46"/>
+      <c r="U4" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="V4" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="W4" s="57" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X4" s="55" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="54">
+      <c r="C5" s="6">
         <v>23</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="6">
         <v>0</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="6" t="s">
         <v>195</v>
       </c>
       <c r="F5" s="7" t="s">
@@ -2366,13 +2494,13 @@
       <c r="H5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="59">
+      <c r="I5" s="5">
         <v>-5.3999999999999999E-2</v>
       </c>
-      <c r="J5" s="54" t="s">
+      <c r="J5" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="K5" s="60" t="s">
+      <c r="K5" s="5" t="s">
         <v>219</v>
       </c>
       <c r="L5" s="17" t="s">
@@ -2381,45 +2509,46 @@
       <c r="N5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="54" t="s">
+      <c r="O5" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="P5" s="54" t="s">
+      <c r="P5" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="Q5" s="54" t="s">
+      <c r="Q5" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="R5" s="54">
+      <c r="R5" s="6">
         <v>0</v>
       </c>
       <c r="S5" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="U5" s="41" t="s">
+      <c r="U5" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="V5" s="41"/>
-      <c r="W5" s="41"/>
-    </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B6" s="41" t="s">
+      <c r="V5" s="45"/>
+      <c r="W5" s="45"/>
+      <c r="X5" s="46"/>
+    </row>
+    <row r="6" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B6" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
       <c r="H6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="60" t="s">
+      <c r="I6" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J6" s="54" t="s">
+      <c r="J6" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="K6" s="60" t="s">
+      <c r="K6" s="5" t="s">
         <v>220</v>
       </c>
       <c r="L6" s="16" t="s">
@@ -2428,16 +2557,16 @@
       <c r="N6" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="O6" s="54" t="s">
+      <c r="O6" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="P6" s="54" t="s">
+      <c r="P6" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="6">
         <v>1</v>
       </c>
-      <c r="R6" s="54" t="s">
+      <c r="R6" s="6" t="s">
         <v>237</v>
       </c>
       <c r="S6" s="7" t="s">
@@ -2452,46 +2581,49 @@
       <c r="W6" s="16" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X6" s="56" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="6">
         <v>0</v>
       </c>
-      <c r="E7" s="54" t="s">
+      <c r="E7" s="6" t="s">
         <v>122</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="H7" s="61" t="s">
+      <c r="H7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="58" t="s">
+      <c r="I7" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J7" s="52" t="s">
+      <c r="J7" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="K7" s="58" t="s">
+      <c r="K7" s="5" t="s">
         <v>221</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="N7" s="41" t="s">
+      <c r="N7" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
       <c r="U7" s="36" t="s">
         <v>160</v>
       </c>
@@ -2501,36 +2633,39 @@
       <c r="W7" s="16" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="56" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E8" s="54" t="s">
+      <c r="E8" s="6" t="s">
         <v>200</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="H8" s="61" t="s">
+      <c r="H8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="52" t="s">
+      <c r="I8" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="J8" s="52" t="s">
+      <c r="J8" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="K8" s="52" t="s">
+      <c r="K8" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="L8" s="62" t="s">
+      <c r="L8" s="7" t="s">
         <v>226</v>
       </c>
       <c r="N8" s="11" t="s">
@@ -2560,33 +2695,36 @@
       <c r="W8" s="35" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="56" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="6" t="s">
         <v>202</v>
       </c>
       <c r="F9" s="7">
         <v>36113586</v>
       </c>
-      <c r="H9" s="63" t="s">
+      <c r="H9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="J9" s="55" t="s">
+      <c r="J9" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="K9" s="64" t="s">
+      <c r="K9" s="14" t="s">
         <v>223</v>
       </c>
       <c r="L9" s="13">
@@ -2601,15 +2739,18 @@
       <c r="W9" s="35" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B10" s="41" t="s">
+      <c r="X9" s="56" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B10" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
       <c r="U10" s="36" t="s">
         <v>154</v>
       </c>
@@ -2619,21 +2760,24 @@
       <c r="W10" s="35" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="56" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B11" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="42">
         <v>0</v>
       </c>
-      <c r="E11" s="55" t="s">
+      <c r="E11" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="F11" s="57" t="s">
+      <c r="F11" s="13" t="s">
         <v>205</v>
       </c>
       <c r="U11" s="36" t="s">
@@ -2645,8 +2789,11 @@
       <c r="W11" s="35" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="56" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.2">
       <c r="U12" s="36" t="s">
         <v>156</v>
       </c>
@@ -2656,8 +2803,11 @@
       <c r="W12" s="35" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="56" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24" x14ac:dyDescent="0.2">
       <c r="U13" s="36" t="s">
         <v>162</v>
       </c>
@@ -2667,8 +2817,11 @@
       <c r="W13" s="35" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="56" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24" x14ac:dyDescent="0.2">
       <c r="U14" s="36" t="s">
         <v>161</v>
       </c>
@@ -2678,15 +2831,19 @@
       <c r="W14" s="35" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="U15" s="48" t="s">
+      <c r="X14" s="56" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="U15" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="V15" s="43"/>
-      <c r="W15" s="44"/>
-    </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V15" s="45"/>
+      <c r="W15" s="45"/>
+      <c r="X15" s="46"/>
+    </row>
+    <row r="16" spans="2:24" x14ac:dyDescent="0.2">
       <c r="U16" s="36" t="s">
         <v>154</v>
       </c>
@@ -2696,8 +2853,11 @@
       <c r="W16" s="16" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="17" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="56" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="17" spans="21:24" x14ac:dyDescent="0.2">
       <c r="U17" s="36" t="s">
         <v>241</v>
       </c>
@@ -2707,8 +2867,11 @@
       <c r="W17" s="16" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="18" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="56" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" spans="21:24" x14ac:dyDescent="0.2">
       <c r="U18" s="36" t="s">
         <v>156</v>
       </c>
@@ -2718,8 +2881,11 @@
       <c r="W18" s="16" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="19" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="56" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="21:24" x14ac:dyDescent="0.2">
       <c r="U19" s="36" t="s">
         <v>160</v>
       </c>
@@ -2729,8 +2895,11 @@
       <c r="W19" s="35" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="20" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="56" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20" spans="21:24" x14ac:dyDescent="0.2">
       <c r="U20" s="36" t="s">
         <v>161</v>
       </c>
@@ -2740,8 +2909,11 @@
       <c r="W20" s="35" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="56" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="21" spans="21:24" x14ac:dyDescent="0.2">
       <c r="U21" s="36" t="s">
         <v>157</v>
       </c>
@@ -2751,8 +2923,11 @@
       <c r="W21" s="35" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="22" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="56" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="22" spans="21:24" x14ac:dyDescent="0.2">
       <c r="U22" s="36" t="s">
         <v>158</v>
       </c>
@@ -2762,8 +2937,11 @@
       <c r="W22" s="35" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="23" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="56" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="23" spans="21:24" x14ac:dyDescent="0.2">
       <c r="U23" s="36" t="s">
         <v>162</v>
       </c>
@@ -2773,8 +2951,11 @@
       <c r="W23" s="35" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="24" spans="21:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="56" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="24" spans="21:24" x14ac:dyDescent="0.2">
       <c r="U24" s="38" t="s">
         <v>159</v>
       </c>
@@ -2784,18 +2965,21 @@
       <c r="W24" s="40" t="s">
         <v>260</v>
       </c>
+      <c r="X24" s="58" t="s">
+        <v>260</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="U5:W5"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="U5:X5"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="U15:X15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2854,14 +3038,14 @@
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
       <c r="M5" s="2" t="s">
         <v>2</v>
       </c>
@@ -2879,11 +3063,11 @@
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
       <c r="F6" s="4" t="s">
         <v>87</v>
       </c>
@@ -2902,13 +3086,13 @@
       <c r="K6" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="M6" s="41" t="s">
+      <c r="M6" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B7" s="8" t="s">
@@ -2964,21 +3148,21 @@
       <c r="D8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="42" t="s">
+      <c r="F8" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="47"/>
-      <c r="M8" s="48" t="s">
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="49"/>
+      <c r="M8" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="44"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="45"/>
+      <c r="Q8" s="46"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
@@ -3057,9 +3241,9 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
       <c r="F11" s="6"/>
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>
@@ -3276,14 +3460,14 @@
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
       <c r="M5" s="2" t="s">
         <v>2</v>
       </c>
@@ -3301,11 +3485,11 @@
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
       <c r="F6" s="23" t="s">
         <v>87</v>
       </c>
@@ -3324,13 +3508,13 @@
       <c r="K6" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="M6" s="41" t="s">
+      <c r="M6" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B7" s="8" t="s">
@@ -3386,21 +3570,21 @@
       <c r="D8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="F8" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="51"/>
-      <c r="M8" s="48" t="s">
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="54"/>
+      <c r="M8" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="44"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="45"/>
+      <c r="Q8" s="46"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
@@ -3482,9 +3666,9 @@
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
       <c r="F11" s="6"/>
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>

--- a/R/Scripts/matings/genus_results.xlsx
+++ b/R/Scripts/matings/genus_results.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucascamacho/Dropbox/Doc/Code/evowm/R/Scripts/matings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014A016F-172F-374C-AA4F-44586086DD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6A10DB-F7FC-F544-9276-1084251C48F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{41D2D77F-E09E-6C4F-BC4A-8BBD63B28252}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{41D2D77F-E09E-6C4F-BC4A-8BBD63B28252}"/>
   </bookViews>
   <sheets>
-    <sheet name="FM" sheetId="1" r:id="rId1"/>
-    <sheet name="normal" sheetId="4" r:id="rId2"/>
+    <sheet name="normal" sheetId="4" r:id="rId1"/>
+    <sheet name="FM" sheetId="1" r:id="rId2"/>
     <sheet name="integration" sheetId="2" r:id="rId3"/>
     <sheet name="size" sheetId="3" r:id="rId4"/>
   </sheets>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="311">
   <si>
     <t>PGLS</t>
   </si>
@@ -242,51 +242,15 @@
     <t>Platyrrhini (N = 16)</t>
   </si>
   <si>
-    <t>NMDS1 + NMDS2 + Integration + Size</t>
-  </si>
-  <si>
-    <t>-75.2</t>
-  </si>
-  <si>
     <t>-74.2</t>
   </si>
   <si>
-    <t>0.000000019</t>
-  </si>
-  <si>
-    <t>NMDS1 + NMDS2 + Integration</t>
-  </si>
-  <si>
     <t>0.067</t>
   </si>
   <si>
-    <t>10.2</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>0.000018</t>
-  </si>
-  <si>
-    <t>1.24</t>
-  </si>
-  <si>
-    <t>1.45</t>
-  </si>
-  <si>
     <t>-61.6</t>
   </si>
   <si>
-    <t>-60.3</t>
-  </si>
-  <si>
-    <t>-59.7</t>
-  </si>
-  <si>
-    <t>0.0000315</t>
-  </si>
-  <si>
     <t>-0.60</t>
   </si>
   <si>
@@ -383,45 +347,9 @@
     <t>0.22</t>
   </si>
   <si>
-    <t>23.4</t>
-  </si>
-  <si>
-    <t>0.000016</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>5.82</t>
-  </si>
-  <si>
-    <t>6.48</t>
-  </si>
-  <si>
-    <t>7.71</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>1.89</t>
-  </si>
-  <si>
-    <t>47.89</t>
-  </si>
-  <si>
-    <t>0.014</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>8.133</t>
-  </si>
-  <si>
-    <t>0.0000057</t>
-  </si>
-  <si>
     <t>14.18</t>
   </si>
   <si>
@@ -476,30 +404,6 @@
     <t>1.25</t>
   </si>
   <si>
-    <t>0.00000617</t>
-  </si>
-  <si>
-    <t>6.11</t>
-  </si>
-  <si>
-    <t>0.0693</t>
-  </si>
-  <si>
-    <t>Size + NMDS1 + NMDS2 + Integration</t>
-  </si>
-  <si>
-    <t>6.60</t>
-  </si>
-  <si>
-    <t>0.4</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>8.365</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -617,48 +521,12 @@
     <t>Phylogenetic Half-Life (Myr)</t>
   </si>
   <si>
-    <t>Integration + NMDS1 + NMDS2</t>
-  </si>
-  <si>
-    <t>Integration + NMDS1 + NMDS2 + Size</t>
-  </si>
-  <si>
     <t>OU model selection across primates clades (ΔAICc &lt; 2)</t>
   </si>
   <si>
-    <t>0.0000073</t>
-  </si>
-  <si>
-    <t>884889.2</t>
-  </si>
-  <si>
-    <t>6.43</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>0.0144</t>
-  </si>
-  <si>
-    <t>0.0851</t>
-  </si>
-  <si>
-    <t>8.13</t>
-  </si>
-  <si>
-    <t>0.00000019</t>
-  </si>
-  <si>
     <t>22.2</t>
   </si>
   <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>11.45</t>
-  </si>
-  <si>
     <t xml:space="preserve">Estimate </t>
   </si>
   <si>
@@ -903,6 +771,207 @@
   </si>
   <si>
     <t>0.700</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Predictors</t>
+  </si>
+  <si>
+    <t>Models</t>
+  </si>
+  <si>
+    <t>OU models slopes and SE</t>
+  </si>
+  <si>
+    <t>-0.51 ± 0.086</t>
+  </si>
+  <si>
+    <t>-0.19 ± 0.044</t>
+  </si>
+  <si>
+    <t>-0.34 ± 0.060</t>
+  </si>
+  <si>
+    <t>-0.19 ± 0.04</t>
+  </si>
+  <si>
+    <t>-0.19 ± 0.041</t>
+  </si>
+  <si>
+    <t>0.019 ± 0.054</t>
+  </si>
+  <si>
+    <t>Integration + Size + NMDS1 + NMDS2</t>
+  </si>
+  <si>
+    <t>25.4</t>
+  </si>
+  <si>
+    <t>27.4</t>
+  </si>
+  <si>
+    <t>1.98</t>
+  </si>
+  <si>
+    <t>0.0247</t>
+  </si>
+  <si>
+    <t>28.02</t>
+  </si>
+  <si>
+    <t>0.000020</t>
+  </si>
+  <si>
+    <t>-0.50 ± 0.091</t>
+  </si>
+  <si>
+    <t>-0.15 ± 0.054</t>
+  </si>
+  <si>
+    <t>-0.08 ± 0.069</t>
+  </si>
+  <si>
+    <t>-0.03 ±0.064</t>
+  </si>
+  <si>
+    <t>3.11</t>
+  </si>
+  <si>
+    <t>18.04082</t>
+  </si>
+  <si>
+    <t>0.0384</t>
+  </si>
+  <si>
+    <t>0.0607</t>
+  </si>
+  <si>
+    <t>11.407</t>
+  </si>
+  <si>
+    <t>0.019 ± 0.046</t>
+  </si>
+  <si>
+    <t>-74.9</t>
+  </si>
+  <si>
+    <t>0.00000969</t>
+  </si>
+  <si>
+    <t>714897.4</t>
+  </si>
+  <si>
+    <t>0.0183</t>
+  </si>
+  <si>
+    <t>37.75957</t>
+  </si>
+  <si>
+    <t>-0.046 ± 0.008</t>
+  </si>
+  <si>
+    <t>-0.018 ± 0.004</t>
+  </si>
+  <si>
+    <t>-0.0055 ± 0.006</t>
+  </si>
+  <si>
+    <t>-0.0030 ± 0.005</t>
+  </si>
+  <si>
+    <t>-0.052 ± 0.0081</t>
+  </si>
+  <si>
+    <t>-63.2</t>
+  </si>
+  <si>
+    <t>1.64</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>-0.023 ± 0.005</t>
+  </si>
+  <si>
+    <t>10.24837</t>
+  </si>
+  <si>
+    <t>-0.024 ± 0.006</t>
+  </si>
+  <si>
+    <t>-0.022 ± 0.0037</t>
+  </si>
+  <si>
+    <t>0.0032 ± 0.0043</t>
+  </si>
+  <si>
+    <t>0.013 ± 0.0050</t>
+  </si>
+  <si>
+    <t>16.4405</t>
+  </si>
+  <si>
+    <t>0.0421</t>
+  </si>
+  <si>
+    <t>-0.037 ± 0.006</t>
+  </si>
+  <si>
+    <t>-0,021 ± 0.003</t>
+  </si>
+  <si>
+    <t>0.0032 ± 0.005</t>
+  </si>
+  <si>
+    <t>0.0034 ± 0.004</t>
+  </si>
+  <si>
+    <t>28.02084</t>
+  </si>
+  <si>
+    <t>3.38</t>
+  </si>
+  <si>
+    <t>22.4</t>
+  </si>
+  <si>
+    <t>11.55245</t>
+  </si>
+  <si>
+    <t>-0.34 ± 0.06</t>
+  </si>
+  <si>
+    <t>0.019 ± 0.055</t>
+  </si>
+  <si>
+    <t>0.020 ± 0.046</t>
+  </si>
+  <si>
+    <t>25.8</t>
+  </si>
+  <si>
+    <t>-0.50 ± 0.086</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>10.9329</t>
+  </si>
+  <si>
+    <t>0.0634</t>
+  </si>
+  <si>
+    <t>-0.33 ± 0.06</t>
+  </si>
+  <si>
+    <t>0.022 ± 0.05</t>
+  </si>
+  <si>
+    <t>0.019 ± 0.04</t>
   </si>
 </sst>
 </file>
@@ -1142,7 +1211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1268,6 +1337,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1304,19 +1382,79 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1652,25 +1790,868 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C0EB34-5C4A-D443-A1F7-912E9592B05E}">
+  <dimension ref="B2:AB24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.6640625" customWidth="1"/>
+    <col min="9" max="9" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="26.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B2" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="L2" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="R2" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="41"/>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="58"/>
+      <c r="H3" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="L3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y3" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="54"/>
+      <c r="AB3" s="54"/>
+    </row>
+    <row r="4" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B4" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I4" s="64" t="s">
+        <v>246</v>
+      </c>
+      <c r="J4" s="64"/>
+      <c r="L4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="R4" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="49"/>
+      <c r="Y4" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA4" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB4" s="15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G5" s="59"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="64"/>
+      <c r="L5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="5">
+        <v>-5.3999999999999999E-2</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="P5" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="V5" s="6">
+        <v>0</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y5" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z5" s="48"/>
+      <c r="AA5" s="48"/>
+      <c r="AB5" s="49"/>
+    </row>
+    <row r="6" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="F6" s="13">
+        <v>332697</v>
+      </c>
+      <c r="G6" s="58"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="68" t="s">
+        <v>254</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="P6" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="U6" s="6">
+        <v>1</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y6" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z6" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA6" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="AB6" s="43" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B7" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="69" t="s">
+        <v>248</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="R7" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="S7" s="46"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="46"/>
+      <c r="Y7" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z7" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="AA7" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB7" s="43" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="G8" s="59"/>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="R8" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="S8" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="T8" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="U8" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="V8" s="12">
+        <v>0</v>
+      </c>
+      <c r="W8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y8" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z8" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA8" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB8" s="43" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B9" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="J9" s="63" t="s">
+        <v>263</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="P9" s="13">
+        <v>52</v>
+      </c>
+      <c r="Y9" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z9" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA9" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB9" s="43" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B10" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="42">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="G10" s="58"/>
+      <c r="H10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="J10" s="63" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y10" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z10" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA10" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB10" s="43" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="G11" s="59"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="65"/>
+      <c r="Y11" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z11" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA11" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB11" s="43" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="H12" s="66"/>
+      <c r="I12" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y12" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z12" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA12" s="35" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB12" s="43" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="H13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="J13" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y13" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z13" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA13" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB13" s="43" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="H14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="70" t="s">
+        <v>249</v>
+      </c>
+      <c r="J14" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y14" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z14" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA14" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB14" s="43" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="H15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="J15" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y15" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z15" s="48"/>
+      <c r="AA15" s="48"/>
+      <c r="AB15" s="49"/>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="H16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="J16" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y16" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z16" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA16" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="AB16" s="43" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="8:28" x14ac:dyDescent="0.2">
+      <c r="H17" s="66"/>
+      <c r="I17" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="J17" s="65"/>
+      <c r="Y17" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z17" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="AA17" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="AB17" s="43" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="8:28" x14ac:dyDescent="0.2">
+      <c r="H18" s="66"/>
+      <c r="I18" s="71" t="s">
+        <v>254</v>
+      </c>
+      <c r="J18" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y18" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z18" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA18" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB18" s="43" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="8:28" x14ac:dyDescent="0.2">
+      <c r="H19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="70" t="s">
+        <v>250</v>
+      </c>
+      <c r="J19" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y19" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z19" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA19" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB19" s="43" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="20" spans="8:28" x14ac:dyDescent="0.2">
+      <c r="H20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="J20" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y20" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z20" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA20" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB20" s="43" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="21" spans="8:28" x14ac:dyDescent="0.2">
+      <c r="H21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="J21" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y21" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z21" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA21" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="AB21" s="43" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="8:28" x14ac:dyDescent="0.2">
+      <c r="H22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="J22" s="84" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y22" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z22" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="AA22" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="AB22" s="43" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23" spans="8:28" x14ac:dyDescent="0.2">
+      <c r="Y23" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z23" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA23" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB23" s="43" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="24" spans="8:28" x14ac:dyDescent="0.2">
+      <c r="Y24" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z24" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="AA24" s="40" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB24" s="45" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="Y15:AB15"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="R4:W4"/>
+    <mergeCell ref="R7:W7"/>
+    <mergeCell ref="Y3:AB3"/>
+    <mergeCell ref="Y5:AB5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E042300B-F734-714C-B163-A528E0097BE3}">
-  <dimension ref="B2:V24"/>
+  <dimension ref="B1:AB24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="47.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="19.33203125" customWidth="1"/>
+    <col min="20" max="20" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+    </row>
+    <row r="2" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="M2" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1693,10 +2674,30 @@
         <v>7</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="R3" s="58"/>
+      <c r="S3" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+    </row>
+    <row r="4" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1706,48 +2707,50 @@
       <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="M4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S4" s="15" t="s">
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="M4" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="T4" s="64" t="s">
+        <v>246</v>
+      </c>
+      <c r="U4" s="64"/>
+      <c r="V4" s="60"/>
+      <c r="W4" s="60"/>
+      <c r="Y4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="U4" s="15" t="s">
+      <c r="Z4" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="V4" s="55" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B5" s="43" t="s">
+      <c r="AB4" s="15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B5" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
       <c r="F5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1766,21 +2769,37 @@
       <c r="K5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="43" t="s">
+      <c r="M5" s="75" t="s">
+        <v>254</v>
+      </c>
+      <c r="N5" s="77" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="75">
+        <v>0</v>
+      </c>
+      <c r="P5" s="75" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q5" s="75" t="s">
+        <v>273</v>
+      </c>
+      <c r="R5" s="59"/>
+      <c r="S5" s="66"/>
+      <c r="T5" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="S5" s="50" t="s">
+      <c r="U5" s="64"/>
+      <c r="V5" s="60"/>
+      <c r="W5" s="60"/>
+      <c r="Y5" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="T5" s="45"/>
-      <c r="U5" s="45"/>
-      <c r="V5" s="46"/>
-    </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="Z5" s="48"/>
+      <c r="AA5" s="48"/>
+      <c r="AB5" s="49"/>
+    </row>
+    <row r="6" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B6" s="8" t="s">
         <v>15</v>
       </c>
@@ -1790,43 +2809,53 @@
       <c r="D6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="49"/>
-      <c r="M6" s="4" t="s">
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="52"/>
+      <c r="M6" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>3646655</v>
-      </c>
-      <c r="S6" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="T6" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="U6" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="V6" s="7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="N6" s="78" t="s">
+        <v>271</v>
+      </c>
+      <c r="O6" s="75" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" s="75" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q6" s="75" t="s">
+        <v>275</v>
+      </c>
+      <c r="R6" s="58"/>
+      <c r="S6" s="80"/>
+      <c r="T6" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="V6" s="60"/>
+      <c r="W6" s="60"/>
+      <c r="Y6" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z6" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA6" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB6" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
         <v>18</v>
       </c>
@@ -1854,35 +2883,39 @@
       <c r="K7" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="M7" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="N7" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="O7" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q7" s="22">
-        <v>2196387</v>
-      </c>
-      <c r="S7" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="T7" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="U7" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="V7" s="7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="M7" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T7" s="69" t="s">
+        <v>276</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="V7" s="60"/>
+      <c r="W7" s="60"/>
+      <c r="Y7" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z7" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA7" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB7" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
@@ -1898,27 +2931,47 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
-      <c r="M8" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="N8" s="45"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="46"/>
-      <c r="S8" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="T8" s="59" t="s">
-        <v>171</v>
-      </c>
-      <c r="U8" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="V8" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="M8" s="75" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="78" t="s">
+        <v>281</v>
+      </c>
+      <c r="O8" s="75">
+        <v>0</v>
+      </c>
+      <c r="P8" s="75" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q8" s="75" t="s">
+        <v>266</v>
+      </c>
+      <c r="R8" s="59"/>
+      <c r="S8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T8" s="70" t="s">
+        <v>277</v>
+      </c>
+      <c r="U8" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="V8" s="60"/>
+      <c r="W8" s="60"/>
+      <c r="Y8" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z8" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA8" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB8" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B9" s="11" t="s">
         <v>20</v>
       </c>
@@ -1934,143 +2987,177 @@
       <c r="I9" s="5"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
-      <c r="M9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="S9" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="T9" s="59" t="s">
-        <v>174</v>
-      </c>
-      <c r="U9" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="V9" s="7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
+      <c r="M9" s="79" t="s">
+        <v>254</v>
+      </c>
+      <c r="N9" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="O9" s="66" t="s">
+        <v>282</v>
+      </c>
+      <c r="P9" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q9" s="75" t="s">
+        <v>285</v>
+      </c>
+      <c r="R9" s="59"/>
+      <c r="S9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T9" s="70" t="s">
+        <v>278</v>
+      </c>
+      <c r="U9" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="V9" s="60"/>
+      <c r="W9" s="60"/>
+      <c r="Y9" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z9" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA9" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB9" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
       <c r="F10" s="6"/>
       <c r="G10" s="5"/>
       <c r="H10" s="6"/>
       <c r="I10" s="5"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="58"/>
+      <c r="S10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T10" s="70" t="s">
+        <v>279</v>
+      </c>
+      <c r="U10" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="V10" s="60"/>
+      <c r="W10" s="60"/>
+      <c r="Y10" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z10" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA10" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB10" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="M11" s="79" t="s">
+        <v>254</v>
+      </c>
+      <c r="N11" s="78">
+        <v>-151</v>
+      </c>
+      <c r="O11" s="66">
+        <v>0</v>
+      </c>
+      <c r="P11" s="75" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q11" s="75" t="s">
+        <v>290</v>
+      </c>
+      <c r="R11" s="59"/>
+      <c r="S11" s="66"/>
+      <c r="T11" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="U11" s="65"/>
+      <c r="V11" s="60"/>
+      <c r="W11" s="60"/>
+      <c r="Y11" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z11" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA11" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="AB11" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="S12" s="66"/>
+      <c r="T12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="P10" s="6">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="S10" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="T10" s="59" t="s">
-        <v>174</v>
-      </c>
-      <c r="U10" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="V10" s="7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="M11" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="O11" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="P11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>377592</v>
-      </c>
-      <c r="S11" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="T11" s="59" t="s">
-        <v>181</v>
-      </c>
-      <c r="U11" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="V11" s="7" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="M12" s="6"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="S12" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="T12" s="59" t="s">
-        <v>185</v>
-      </c>
-      <c r="U12" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="V12" s="7" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="U12" s="81" t="s">
+        <v>254</v>
+      </c>
+      <c r="V12" s="60"/>
+      <c r="W12" s="60"/>
+      <c r="Y12" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z12" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA12" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB12" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F13" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="S13" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="T13" s="59" t="s">
-        <v>106</v>
-      </c>
-      <c r="U13" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="S13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T13" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="U13" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="V13" s="60"/>
+      <c r="W13" s="60"/>
+      <c r="Y13" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z13" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA13" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB13" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F14" s="1" t="s">
         <v>9</v>
       </c>
@@ -2086,20 +3173,31 @@
       <c r="J14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="S14" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="T14" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="U14" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="V14" s="7" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="S14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T14" s="70" t="s">
+        <v>284</v>
+      </c>
+      <c r="U14" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="V14" s="60"/>
+      <c r="W14" s="60"/>
+      <c r="Y14" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z14" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA14" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="AB14" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F15" s="8" t="s">
         <v>27</v>
       </c>
@@ -2115,14 +3213,25 @@
       <c r="J15" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="S15" s="50" t="s">
+      <c r="S15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T15" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="V15" s="60"/>
+      <c r="W15" s="60"/>
+      <c r="Y15" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="T15" s="45"/>
-      <c r="U15" s="45"/>
-      <c r="V15" s="46"/>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="Z15" s="48"/>
+      <c r="AA15" s="48"/>
+      <c r="AB15" s="49"/>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.2">
       <c r="F16" s="4" t="s">
         <v>15</v>
       </c>
@@ -2138,20 +3247,31 @@
       <c r="J16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="S16" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="T16" s="59" t="s">
-        <v>167</v>
-      </c>
-      <c r="U16" s="16" t="s">
+      <c r="S16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T16" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="V16" s="60"/>
+      <c r="W16" s="60"/>
+      <c r="Y16" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z16" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA16" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="V16" s="16" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="17" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="AB16" s="16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="6:28" x14ac:dyDescent="0.2">
       <c r="F17" s="4" t="s">
         <v>18</v>
       </c>
@@ -2167,20 +3287,27 @@
       <c r="J17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="S17" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="T17" s="59" t="s">
-        <v>169</v>
-      </c>
-      <c r="U17" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="V17" s="16" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="18" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="S17" s="66"/>
+      <c r="T17" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="U17" s="65"/>
+      <c r="V17" s="60"/>
+      <c r="W17" s="60"/>
+      <c r="Y17" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z17" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA17" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB17" s="16" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="6:28" x14ac:dyDescent="0.2">
       <c r="F18" s="4" t="s">
         <v>19</v>
       </c>
@@ -2196,20 +3323,29 @@
       <c r="J18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="S18" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="T18" s="59" t="s">
-        <v>172</v>
-      </c>
-      <c r="U18" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="V18" s="16" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="19" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="S18" s="66"/>
+      <c r="T18" s="76" t="s">
+        <v>254</v>
+      </c>
+      <c r="U18" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="V18" s="60"/>
+      <c r="W18" s="60"/>
+      <c r="Y18" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z18" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA18" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB18" s="16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="6:28" x14ac:dyDescent="0.2">
       <c r="F19" s="4" t="s">
         <v>20</v>
       </c>
@@ -2225,20 +3361,31 @@
       <c r="J19" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="S19" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="T19" s="59" t="s">
-        <v>176</v>
-      </c>
-      <c r="U19" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="V19" s="7" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="20" spans="6:22" x14ac:dyDescent="0.2">
+      <c r="S19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T19" s="70" t="s">
+        <v>292</v>
+      </c>
+      <c r="U19" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="V19" s="60"/>
+      <c r="W19" s="60"/>
+      <c r="Y19" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z19" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA19" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB19" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="6:28" x14ac:dyDescent="0.2">
       <c r="F20" s="11" t="s">
         <v>31</v>
       </c>
@@ -2254,732 +3401,124 @@
       <c r="J20" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="S20" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="T20" s="59" t="s">
-        <v>178</v>
-      </c>
-      <c r="U20" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="V20" s="7" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="21" spans="6:22" x14ac:dyDescent="0.2">
-      <c r="S21" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="T21" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="U21" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="V21" s="7" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="22" spans="6:22" x14ac:dyDescent="0.2">
-      <c r="S22" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="T22" s="59" t="s">
-        <v>187</v>
-      </c>
-      <c r="U22" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="V22" s="7" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="23" spans="6:22" x14ac:dyDescent="0.2">
-      <c r="S23" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="T23" s="59" t="s">
-        <v>187</v>
-      </c>
-      <c r="U23" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="V23" s="7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="24" spans="6:22" x14ac:dyDescent="0.2">
-      <c r="S24" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="T24" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="U24" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="V24" s="13" t="s">
-        <v>287</v>
+      <c r="S20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T20" s="70" t="s">
+        <v>293</v>
+      </c>
+      <c r="U20" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="V20" s="60"/>
+      <c r="W20" s="60"/>
+      <c r="Y20" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z20" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA20" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB20" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="21" spans="6:28" x14ac:dyDescent="0.2">
+      <c r="S21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="U21" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="V21" s="60"/>
+      <c r="W21" s="60"/>
+      <c r="Y21" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z21" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA21" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB21" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="6:28" x14ac:dyDescent="0.2">
+      <c r="S22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T22" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="U22" s="82" t="s">
+        <v>244</v>
+      </c>
+      <c r="V22" s="62"/>
+      <c r="W22" s="62"/>
+      <c r="Y22" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z22" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA22" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB22" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="23" spans="6:28" x14ac:dyDescent="0.2">
+      <c r="Y23" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z23" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA23" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB23" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24" spans="6:28" x14ac:dyDescent="0.2">
+      <c r="Y24" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z24" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA24" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB24" s="13" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="14">
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="M4:Q4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="M10:Q10"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="Y15:AB15"/>
+    <mergeCell ref="Y5:AB5"/>
     <mergeCell ref="F4:K4"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="M8:Q8"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="F6:K6"/>
-    <mergeCell ref="S15:V15"/>
-    <mergeCell ref="S5:V5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C0EB34-5C4A-D443-A1F7-912E9592B05E}">
-  <dimension ref="B2:X24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="49.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="H2" s="43" t="s">
-        <v>227</v>
-      </c>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="N2" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="41"/>
-    </row>
-    <row r="3" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="U3" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="V3" s="51"/>
-      <c r="W3" s="51"/>
-      <c r="X3" s="51"/>
-    </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B4" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="H4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="L4" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="N4" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="46"/>
-      <c r="U4" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="V4" s="57" t="s">
-        <v>153</v>
-      </c>
-      <c r="W4" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="X4" s="55" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="6">
-        <v>23</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="5">
-        <v>-5.3999999999999999E-2</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="R5" s="6">
-        <v>0</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="U5" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="V5" s="45"/>
-      <c r="W5" s="45"/>
-      <c r="X5" s="46"/>
-    </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B6" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="H6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="L6" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>1</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="S6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="U6" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="V6" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="W6" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="X6" s="56" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="N7" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="U7" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="V7" s="37" t="s">
-        <v>244</v>
-      </c>
-      <c r="W7" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="X7" s="56" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B8" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="O8" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q8" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="R8" s="12">
-        <v>0</v>
-      </c>
-      <c r="S8" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="U8" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="V8" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="W8" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="X8" s="56" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B9" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="F9" s="7">
-        <v>36113586</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="L9" s="13">
-        <v>52</v>
-      </c>
-      <c r="U9" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="V9" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="W9" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="X9" s="56" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B10" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="U10" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="V10" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="W10" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="X10" s="56" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B11" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D11" s="42">
-        <v>0</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="U11" s="36" t="s">
-        <v>241</v>
-      </c>
-      <c r="V11" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="W11" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="X11" s="56" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="U12" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="V12" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="W12" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="X12" s="56" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="U13" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="V13" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="W13" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="X13" s="56" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="U14" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="V14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="W14" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="X14" s="56" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="U15" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="V15" s="45"/>
-      <c r="W15" s="45"/>
-      <c r="X15" s="46"/>
-    </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="U16" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="V16" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="W16" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="X16" s="56" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="17" spans="21:24" x14ac:dyDescent="0.2">
-      <c r="U17" s="36" t="s">
-        <v>241</v>
-      </c>
-      <c r="V17" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="W17" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="X17" s="56" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="18" spans="21:24" x14ac:dyDescent="0.2">
-      <c r="U18" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="V18" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="W18" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="X18" s="56" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="21:24" x14ac:dyDescent="0.2">
-      <c r="U19" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="V19" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="W19" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="X19" s="56" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="20" spans="21:24" x14ac:dyDescent="0.2">
-      <c r="U20" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="V20" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="W20" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="X20" s="56" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="21" spans="21:24" x14ac:dyDescent="0.2">
-      <c r="U21" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="V21" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="W21" s="35" t="s">
-        <v>257</v>
-      </c>
-      <c r="X21" s="56" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="22" spans="21:24" x14ac:dyDescent="0.2">
-      <c r="U22" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="V22" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="W22" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="X22" s="56" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="23" spans="21:24" x14ac:dyDescent="0.2">
-      <c r="U23" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="V23" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="W23" s="35" t="s">
-        <v>259</v>
-      </c>
-      <c r="X23" s="56" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="24" spans="21:24" x14ac:dyDescent="0.2">
-      <c r="U24" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="V24" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="W24" s="40" t="s">
-        <v>260</v>
-      </c>
-      <c r="X24" s="58" t="s">
-        <v>260</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="U5:X5"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="U15:X15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2987,7 +3526,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA526B2-C61A-5F4F-AC86-1A0FD8B06582}">
-  <dimension ref="B3:Q21"/>
+  <dimension ref="B3:T23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="23.1640625" bestFit="1" customWidth="1"/>
@@ -2995,14 +3534,15 @@
     <col min="15" max="15" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.2">
       <c r="F3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
@@ -3027,8 +3567,12 @@
       <c r="M4" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S4" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="T4" s="46"/>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
@@ -3038,14 +3582,14 @@
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
       <c r="M5" s="2" t="s">
         <v>2</v>
       </c>
@@ -3061,18 +3605,24 @@
       <c r="Q5" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B6" s="43" t="s">
+      <c r="S5" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="T5" s="72" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B6" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
       <c r="F6" s="4" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="H6" s="6">
         <v>0</v>
@@ -3081,20 +3631,24 @@
         <v>22</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="M6" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="M6" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="72" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
@@ -3105,13 +3659,13 @@
         <v>16</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>22</v>
@@ -3125,90 +3679,106 @@
       <c r="M7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="6">
-        <v>23</v>
+      <c r="N7" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="O7" s="6">
         <v>0</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>11192242</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="S7" s="66"/>
+      <c r="T7" s="35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="F8" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="49"/>
-      <c r="M8" s="50" t="s">
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="52"/>
+      <c r="M8" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="N8" s="45"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="46"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="49"/>
+      <c r="S8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T8" s="63" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="H9" s="21">
         <v>0</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J9" s="21" t="s">
         <v>42</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>146</v>
+        <v>297</v>
       </c>
       <c r="O9" s="6">
         <v>0</v>
       </c>
-      <c r="P9" s="5">
-        <v>10</v>
+      <c r="P9" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.2">
+        <v>266</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T9" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B10" s="11" t="s">
         <v>20</v>
       </c>
@@ -3216,7 +3786,7 @@
         <v>49</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="5"/>
@@ -3224,58 +3794,81 @@
       <c r="I10" s="5"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
-      <c r="M10" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q10" s="13" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
+      <c r="M10" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" s="65"/>
+      <c r="O10" s="65"/>
+      <c r="P10" s="65"/>
+      <c r="Q10" s="65"/>
+      <c r="S10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T10" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
       <c r="F11" s="6"/>
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="M12" s="6"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="M11" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="N11" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="O11" s="21">
+        <v>0</v>
+      </c>
+      <c r="P11" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q11" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T11" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S12" s="66"/>
+      <c r="T12" s="73" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.2">
       <c r="M13" s="6"/>
       <c r="N13" s="5"/>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S13" s="66"/>
+      <c r="T13" s="35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.2">
       <c r="F14" s="15" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T14" s="86" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B15" s="6"/>
       <c r="F15" s="1" t="s">
         <v>9</v>
@@ -3292,59 +3885,81 @@
       <c r="J15" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T15" s="10" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.2">
       <c r="F16" s="8" t="s">
         <v>27</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="J16" s="17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="S16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T16" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="6:20" x14ac:dyDescent="0.2">
       <c r="F17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>29</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="S17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T17" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18" spans="6:20" x14ac:dyDescent="0.2">
       <c r="F18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="6:10" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+      <c r="S18" s="66"/>
+      <c r="T18" s="74" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="6:20" x14ac:dyDescent="0.2">
       <c r="F19" s="4" t="s">
         <v>19</v>
       </c>
@@ -3352,16 +3967,20 @@
         <v>30</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="6:10" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+      <c r="S19" s="66"/>
+      <c r="T19" s="85" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="20" spans="6:20" x14ac:dyDescent="0.2">
       <c r="F20" s="4" t="s">
         <v>20</v>
       </c>
@@ -3372,13 +3991,19 @@
         <v>63</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="S20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T20" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="6:20" x14ac:dyDescent="0.2">
       <c r="F21" s="11" t="s">
         <v>31</v>
       </c>
@@ -3386,7 +4011,7 @@
         <v>30</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>33</v>
@@ -3394,15 +4019,39 @@
       <c r="J21" s="13" t="s">
         <v>37</v>
       </c>
+      <c r="S21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T21" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="22" spans="6:20" x14ac:dyDescent="0.2">
+      <c r="S22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T22" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="23" spans="6:20" x14ac:dyDescent="0.2">
+      <c r="S23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T23" s="13" t="s">
+        <v>302</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="S4:T4"/>
     <mergeCell ref="F5:K5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="M6:Q6"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="F8:K8"/>
+    <mergeCell ref="M10:Q10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3410,21 +4059,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312CDA36-46BD-4D46-A4C1-BA2213FB6E12}">
-  <dimension ref="B3:Q21"/>
+  <dimension ref="B3:T23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="31.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.2">
       <c r="F3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
@@ -3449,8 +4099,12 @@
       <c r="M4" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S4" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="T4" s="46"/>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
@@ -3460,14 +4114,14 @@
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
       <c r="M5" s="2" t="s">
         <v>2</v>
       </c>
@@ -3483,40 +4137,50 @@
       <c r="Q5" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B6" s="43" t="s">
+      <c r="S5" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="T5" s="72" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B6" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
       <c r="F6" s="23" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H6" s="25">
         <v>0</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J6" s="25" t="s">
         <v>35</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="M6" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="M6" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="72" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
@@ -3527,13 +4191,13 @@
         <v>16</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>22</v>
@@ -3548,97 +4212,113 @@
         <v>15</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>114</v>
+        <v>303</v>
       </c>
       <c r="O7" s="6">
         <v>0</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>5463337</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="S7" s="66"/>
+      <c r="T7" s="35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="52" t="s">
+      <c r="F8" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="54"/>
-      <c r="M8" s="50" t="s">
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="57"/>
+      <c r="M8" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="N8" s="45"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="46"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="49"/>
+      <c r="S8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T8" s="63" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H9" s="29">
         <v>0</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J9" s="29" t="s">
         <v>42</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="M9" s="8" t="s">
         <v>18</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>117</v>
+        <v>265</v>
       </c>
       <c r="O9" s="9">
         <v>0</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>122</v>
+        <v>267</v>
       </c>
       <c r="Q9" s="34" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.2">
+        <v>266</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T9" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="5"/>
@@ -3647,70 +4327,85 @@
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" t="s">
-        <v>116</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q10" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
+        <v>102</v>
+      </c>
+      <c r="M10" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="S10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T10" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
       <c r="F11" s="6"/>
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
-      <c r="M11" s="11" t="s">
-        <v>71</v>
+      <c r="M11" s="19" t="s">
+        <v>254</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="O11" s="12" t="s">
-        <v>121</v>
+        <v>305</v>
+      </c>
+      <c r="O11" s="12">
+        <v>0</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>1192334</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="M12" s="6"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="6"/>
+        <v>307</v>
+      </c>
+      <c r="Q11" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T11" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.2">
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S12" s="66"/>
+      <c r="T12" s="73" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.2">
       <c r="M13" s="6"/>
       <c r="N13" s="5"/>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S13" s="66"/>
+      <c r="T13" s="85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.2">
       <c r="F14" s="15" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T14" s="86" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B15" s="6"/>
       <c r="F15" s="1" t="s">
         <v>9</v>
@@ -3727,30 +4422,42 @@
       <c r="J15" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T15" s="10" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.2">
       <c r="F16" s="8" t="s">
         <v>27</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="J16" s="17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="S16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T16" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="6:20" x14ac:dyDescent="0.2">
       <c r="F17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>29</v>
@@ -3761,59 +4468,79 @@
       <c r="J17" s="17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="S17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T17" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18" spans="6:20" x14ac:dyDescent="0.2">
       <c r="F18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="S18" s="66"/>
+      <c r="T18" s="74" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="6:20" x14ac:dyDescent="0.2">
       <c r="F19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="S19" s="66"/>
+      <c r="T19" s="75" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="20" spans="6:20" x14ac:dyDescent="0.2">
       <c r="F20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="J20" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="6:10" x14ac:dyDescent="0.2">
+      <c r="S20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T20" s="10" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="21" spans="6:20" x14ac:dyDescent="0.2">
       <c r="F21" s="11" t="s">
         <v>31</v>
       </c>
@@ -3821,17 +4548,41 @@
         <v>30</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="J21" s="13" t="s">
         <v>23</v>
       </c>
+      <c r="S21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T21" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="22" spans="6:20" x14ac:dyDescent="0.2">
+      <c r="S22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T22" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="23" spans="6:20" x14ac:dyDescent="0.2">
+      <c r="S23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T23" s="13" t="s">
+        <v>310</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="M10:Q10"/>
+    <mergeCell ref="S4:T4"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="F5:K5"/>
